--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0645B141-A789-4751-B35F-CBE6EE8CDF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAFB6C-9865-4811-90A6-D33C69D47F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,10 @@
   </si>
   <si>
     <t>玩家3普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物韧性被打空对自己释放易伤</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -844,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1170,28 +1174,28 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="2">
+      <c r="A24" s="1">
+        <v>25010001</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="1">
+        <v>0</v>
+      </c>
+      <c r="D24" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -1199,13 +1203,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>127</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1213,13 +1217,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1227,13 +1231,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
+        <v>128</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -1241,13 +1245,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1255,10 +1259,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>20001</v>
+        <v>10302</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1269,10 +1273,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1283,10 +1287,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>4000001</v>
+        <v>30001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1297,38 +1301,38 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>6000001</v>
+        <v>5000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>6010001</v>
+        <v>6000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1339,24 +1343,24 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>7000001</v>
+        <v>6010001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>7010001</v>
+        <v>7000001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1367,24 +1371,24 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>8000001</v>
+        <v>7010001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>8010001</v>
+        <v>8000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1395,24 +1399,24 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>9000001</v>
+        <v>8010001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>10010001</v>
+        <v>9000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1423,10 +1427,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>10020001</v>
+        <v>10010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1437,10 +1441,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>11010001</v>
+        <v>10020001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1451,10 +1455,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>54010001</v>
+        <v>11010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>54030001</v>
+        <v>54010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1479,10 +1483,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1493,10 +1497,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1507,10 +1511,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1521,10 +1525,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1535,10 +1539,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1549,10 +1553,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1563,10 +1567,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1577,10 +1581,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1591,10 +1595,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1605,10 +1609,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1619,10 +1623,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1633,10 +1637,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>55010001</v>
+        <v>54250001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1647,10 +1651,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>55020001</v>
+        <v>55010001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1661,10 +1665,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>55030001</v>
+        <v>55020001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1675,10 +1679,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>55040001</v>
+        <v>55030001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1689,10 +1693,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>55050001</v>
+        <v>55040001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1703,10 +1707,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>55060001</v>
+        <v>55050001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1717,10 +1721,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>55070001</v>
+        <v>55060001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1731,10 +1735,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>56010001</v>
+        <v>55070001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1745,10 +1749,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>56040001</v>
+        <v>56010001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1759,10 +1763,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1773,10 +1777,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1787,10 +1791,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1801,10 +1805,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>57010001</v>
+        <v>56100001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1815,10 +1819,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>57040001</v>
+        <v>57010001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1829,10 +1833,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1843,10 +1847,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1857,10 +1861,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1871,10 +1875,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1885,10 +1889,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>58010001</v>
+        <v>57120001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1899,10 +1903,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>58040001</v>
+        <v>58010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1913,10 +1917,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1927,10 +1931,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1941,10 +1945,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1955,10 +1959,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>59010001</v>
+        <v>58110001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1969,10 +1973,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1983,10 +1987,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -1997,10 +2001,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2011,10 +2015,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2025,10 +2029,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2039,10 +2043,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2053,10 +2057,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2067,10 +2071,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2095,10 +2099,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2109,10 +2113,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>60010001</v>
+        <v>59220001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2123,10 +2127,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2137,10 +2141,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2151,10 +2155,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2165,10 +2169,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2179,10 +2183,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>61020001</v>
+        <v>60110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2193,10 +2197,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2207,10 +2211,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2221,10 +2225,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2235,10 +2239,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2249,10 +2253,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2263,10 +2267,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2277,10 +2281,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2291,22 +2295,36 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C104" s="2">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
         <v>61180001</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B105" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C104" s="2">
-        <v>0</v>
-      </c>
-      <c r="D104" s="2">
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D82" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:D29">
-    <sortCondition ref="A24:A29"/>
+  <autoFilter ref="A4:D83" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D30">
+    <sortCondition ref="A25:A30"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AAFB6C-9865-4811-90A6-D33C69D47F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5B5218-4B61-4843-ABD7-040C61B57EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,15 +91,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30010101,30010102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>30020101,30020102,30020103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30030101,30030102,30030103,30030104</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -870,13 +862,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,7 +896,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -912,7 +904,7 @@
         <v>5010001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -926,7 +918,7 @@
         <v>5020001</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -940,7 +932,7 @@
         <v>5030001</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -954,7 +946,7 @@
         <v>20010001</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1">
         <v>990102</v>
@@ -968,10 +960,10 @@
         <v>20020001</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -982,10 +974,10 @@
         <v>20030001</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -996,10 +988,10 @@
         <v>20040001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1010,10 +1002,10 @@
         <v>20050001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1024,10 +1016,10 @@
         <v>20060001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1038,10 +1030,10 @@
         <v>20070001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1052,10 +1044,10 @@
         <v>20080001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1066,10 +1058,10 @@
         <v>20090001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1080,10 +1072,10 @@
         <v>20100001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1094,10 +1086,10 @@
         <v>20110001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1108,10 +1100,10 @@
         <v>20120001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1122,10 +1114,10 @@
         <v>20130001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1136,10 +1128,10 @@
         <v>20140001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1150,10 +1142,10 @@
         <v>20150001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1164,10 +1156,10 @@
         <v>20160001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1178,7 +1170,7 @@
         <v>25010001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -1206,7 +1198,7 @@
         <v>10102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1223,7 +1215,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1234,7 +1226,7 @@
         <v>10202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1251,7 +1243,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1262,7 +1254,7 @@
         <v>10302</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1290,7 +1282,7 @@
         <v>30001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1304,7 +1296,7 @@
         <v>4000001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1318,7 +1310,7 @@
         <v>5000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1332,7 +1324,7 @@
         <v>6000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1346,7 +1338,7 @@
         <v>6010001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -1360,7 +1352,7 @@
         <v>7000001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1374,7 +1366,7 @@
         <v>7010001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1388,7 +1380,7 @@
         <v>8000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1402,7 +1394,7 @@
         <v>8010001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1416,7 +1408,7 @@
         <v>9000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1430,7 +1422,7 @@
         <v>10010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1444,7 +1436,7 @@
         <v>10020001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1458,7 +1450,7 @@
         <v>11010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1472,7 +1464,7 @@
         <v>54010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1486,7 +1478,7 @@
         <v>54030001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1500,7 +1492,7 @@
         <v>54050001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1514,7 +1506,7 @@
         <v>54070001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1528,7 +1520,7 @@
         <v>54090001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1542,7 +1534,7 @@
         <v>54110001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1556,7 +1548,7 @@
         <v>54130001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1570,7 +1562,7 @@
         <v>54150001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1584,7 +1576,7 @@
         <v>54170001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1598,7 +1590,7 @@
         <v>54190001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1612,7 +1604,7 @@
         <v>54210001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1626,7 +1618,7 @@
         <v>54230001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1640,7 +1632,7 @@
         <v>54250001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1654,7 +1646,7 @@
         <v>55010001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1668,7 +1660,7 @@
         <v>55020001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1682,7 +1674,7 @@
         <v>55030001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1696,7 +1688,7 @@
         <v>55040001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1710,7 +1702,7 @@
         <v>55050001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1724,7 +1716,7 @@
         <v>55060001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1738,7 +1730,7 @@
         <v>55070001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1752,7 +1744,7 @@
         <v>56010001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1766,7 +1758,7 @@
         <v>56040001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1780,7 +1772,7 @@
         <v>56060001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1794,7 +1786,7 @@
         <v>56080001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1808,7 +1800,7 @@
         <v>56100001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1822,7 +1814,7 @@
         <v>57010001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1836,7 +1828,7 @@
         <v>57040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1850,7 +1842,7 @@
         <v>57060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1864,7 +1856,7 @@
         <v>57080001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1878,7 +1870,7 @@
         <v>57100001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1892,7 +1884,7 @@
         <v>57120001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1906,7 +1898,7 @@
         <v>58010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1920,7 +1912,7 @@
         <v>58040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1934,7 +1926,7 @@
         <v>58060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1948,7 +1940,7 @@
         <v>58080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1962,7 +1954,7 @@
         <v>58110001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1976,7 +1968,7 @@
         <v>59010001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1990,7 +1982,7 @@
         <v>59030001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2004,7 +1996,7 @@
         <v>59050001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2018,7 +2010,7 @@
         <v>59070001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2032,7 +2024,7 @@
         <v>59090001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2046,7 +2038,7 @@
         <v>59110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2060,7 +2052,7 @@
         <v>59130001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2074,7 +2066,7 @@
         <v>59150001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2088,7 +2080,7 @@
         <v>59180001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2102,7 +2094,7 @@
         <v>59200001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2116,7 +2108,7 @@
         <v>59220001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2130,7 +2122,7 @@
         <v>60010001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2144,7 +2136,7 @@
         <v>60030001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2158,7 +2150,7 @@
         <v>60060001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2172,7 +2164,7 @@
         <v>60090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2186,7 +2178,7 @@
         <v>60110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2200,7 +2192,7 @@
         <v>61020001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2214,7 +2206,7 @@
         <v>61040001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2228,7 +2220,7 @@
         <v>61060001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2242,7 +2234,7 @@
         <v>61080001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2256,7 +2248,7 @@
         <v>61100001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2270,7 +2262,7 @@
         <v>61120001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2284,7 +2276,7 @@
         <v>61140001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2298,7 +2290,7 @@
         <v>61160001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2312,7 +2304,7 @@
         <v>61180001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA5B5218-4B61-4843-ABD7-040C61B57EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B54382-BEA2-4265-85C1-FAF6A456B3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,10 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>30020101,30020102,30020103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>INT_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -444,6 +440,10 @@
   </si>
   <si>
     <t>怪物韧性被打空对自己释放易伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002010101,3002010201</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +549,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -559,6 +559,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -862,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -896,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,7 +905,7 @@
         <v>5010001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -918,7 +919,7 @@
         <v>5020001</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <v>0</v>
@@ -932,7 +933,7 @@
         <v>5030001</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -946,7 +947,7 @@
         <v>20010001</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="1">
         <v>990102</v>
@@ -960,10 +961,10 @@
         <v>20020001</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -974,10 +975,10 @@
         <v>20030001</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -988,10 +989,10 @@
         <v>20040001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1002,10 +1003,10 @@
         <v>20050001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1016,10 +1017,10 @@
         <v>20060001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1030,10 +1031,10 @@
         <v>20070001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1044,10 +1045,10 @@
         <v>20080001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1058,10 +1059,10 @@
         <v>20090001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1072,10 +1073,10 @@
         <v>20100001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1086,10 +1087,10 @@
         <v>20110001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1100,10 +1101,10 @@
         <v>20120001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1114,10 +1115,10 @@
         <v>20130001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1128,10 +1129,10 @@
         <v>20140001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1142,10 +1143,10 @@
         <v>20150001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1156,10 +1157,10 @@
         <v>20160001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1170,7 +1171,7 @@
         <v>25010001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="1">
         <v>0</v>
@@ -1186,8 +1187,8 @@
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>14</v>
+      <c r="C25" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D25" s="2">
         <v>0</v>
@@ -1198,7 +1199,7 @@
         <v>10102</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
@@ -1214,8 +1215,8 @@
       <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>14</v>
+      <c r="C27" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1226,7 +1227,7 @@
         <v>10202</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -1242,8 +1243,8 @@
       <c r="B29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>14</v>
+      <c r="C29" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1254,7 +1255,7 @@
         <v>10302</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1282,7 +1283,7 @@
         <v>30001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1296,7 +1297,7 @@
         <v>4000001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1310,7 +1311,7 @@
         <v>5000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1324,7 +1325,7 @@
         <v>6000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1338,7 +1339,7 @@
         <v>6010001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -1352,7 +1353,7 @@
         <v>7000001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1366,7 +1367,7 @@
         <v>7010001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1380,7 +1381,7 @@
         <v>8000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1394,7 +1395,7 @@
         <v>8010001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1408,7 +1409,7 @@
         <v>9000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1422,7 +1423,7 @@
         <v>10010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1436,7 +1437,7 @@
         <v>10020001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1450,7 +1451,7 @@
         <v>11010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1464,7 +1465,7 @@
         <v>54010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1478,7 +1479,7 @@
         <v>54030001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1492,7 +1493,7 @@
         <v>54050001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1506,7 +1507,7 @@
         <v>54070001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1520,7 +1521,7 @@
         <v>54090001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1534,7 +1535,7 @@
         <v>54110001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1548,7 +1549,7 @@
         <v>54130001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1562,7 +1563,7 @@
         <v>54150001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1576,7 +1577,7 @@
         <v>54170001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1590,7 +1591,7 @@
         <v>54190001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1604,7 +1605,7 @@
         <v>54210001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1618,7 +1619,7 @@
         <v>54230001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1632,7 +1633,7 @@
         <v>54250001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1646,7 +1647,7 @@
         <v>55010001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1660,7 +1661,7 @@
         <v>55020001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1674,7 +1675,7 @@
         <v>55030001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1688,7 +1689,7 @@
         <v>55040001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1702,7 +1703,7 @@
         <v>55050001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1716,7 +1717,7 @@
         <v>55060001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1730,7 +1731,7 @@
         <v>55070001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1744,7 +1745,7 @@
         <v>56010001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1758,7 +1759,7 @@
         <v>56040001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1772,7 +1773,7 @@
         <v>56060001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1786,7 +1787,7 @@
         <v>56080001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1800,7 +1801,7 @@
         <v>56100001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1814,7 +1815,7 @@
         <v>57010001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1828,7 +1829,7 @@
         <v>57040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1842,7 +1843,7 @@
         <v>57060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1856,7 +1857,7 @@
         <v>57080001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1870,7 +1871,7 @@
         <v>57100001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1884,7 +1885,7 @@
         <v>57120001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1898,7 +1899,7 @@
         <v>58010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1912,7 +1913,7 @@
         <v>58040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1926,7 +1927,7 @@
         <v>58060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1940,7 +1941,7 @@
         <v>58080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1954,7 +1955,7 @@
         <v>58110001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1968,7 +1969,7 @@
         <v>59010001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1982,7 +1983,7 @@
         <v>59030001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -1996,7 +1997,7 @@
         <v>59050001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2010,7 +2011,7 @@
         <v>59070001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2024,7 +2025,7 @@
         <v>59090001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2038,7 +2039,7 @@
         <v>59110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2052,7 +2053,7 @@
         <v>59130001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2066,7 +2067,7 @@
         <v>59150001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2080,7 +2081,7 @@
         <v>59180001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2094,7 +2095,7 @@
         <v>59200001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2108,7 +2109,7 @@
         <v>59220001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2122,7 +2123,7 @@
         <v>60010001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2136,7 +2137,7 @@
         <v>60030001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2150,7 +2151,7 @@
         <v>60060001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2164,7 +2165,7 @@
         <v>60090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2178,7 +2179,7 @@
         <v>60110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2192,7 +2193,7 @@
         <v>61020001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2206,7 +2207,7 @@
         <v>61040001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2220,7 +2221,7 @@
         <v>61060001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2234,7 +2235,7 @@
         <v>61080001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2248,7 +2249,7 @@
         <v>61100001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2262,7 +2263,7 @@
         <v>61120001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2276,7 +2277,7 @@
         <v>61140001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2290,7 +2291,7 @@
         <v>61160001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2304,7 +2305,7 @@
         <v>61180001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B54382-BEA2-4265-85C1-FAF6A456B3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675CF6B9-4BCB-4B1E-A0D1-E59075E23A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,7 +443,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3002010101,3002010201</t>
+    <t>100201011,100201021</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675CF6B9-4BCB-4B1E-A0D1-E59075E23A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EC847A-03AF-4614-A71A-6FA9AC87AF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -444,6 +444,10 @@
   </si>
   <si>
     <t>100201011,100201021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -841,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -902,7 +906,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>5010001</v>
+        <v>955001008</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -916,7 +920,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>5020001</v>
+        <v>955001004</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -930,41 +934,41 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>5030001</v>
+        <v>955001006</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <v>31000030</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>20010001</v>
+        <v>5030001</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>990102</v>
+        <v>0</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>20020001</v>
+        <v>20010001</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="1">
+        <v>990102</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -972,13 +976,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>20030001</v>
+        <v>20020001</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -986,13 +990,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>20040001</v>
+        <v>20030001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1000,13 +1004,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>20050001</v>
+        <v>20040001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1014,13 +1018,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>20060001</v>
+        <v>20050001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1028,13 +1032,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>20070001</v>
+        <v>20060001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1042,13 +1046,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>20080001</v>
+        <v>20070001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1056,13 +1060,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>20090001</v>
+        <v>20080001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1070,13 +1074,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>20100001</v>
+        <v>20090001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1084,13 +1088,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>20110001</v>
+        <v>20100001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1098,13 +1102,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>20120001</v>
+        <v>20110001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1112,13 +1116,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>20130001</v>
+        <v>20120001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1126,13 +1130,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20140001</v>
+        <v>20130001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1140,13 +1144,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>20150001</v>
+        <v>20140001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1154,13 +1158,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>20160001</v>
+        <v>20150001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1168,41 +1172,41 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
+        <v>20160001</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>25010001</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="1">
-        <v>0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1210,13 +1214,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -1224,13 +1228,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -1238,13 +1242,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
       </c>
       <c r="D29" s="2">
         <v>0</v>
@@ -1252,13 +1256,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>
@@ -1266,10 +1270,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>20001</v>
+        <v>10302</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -1280,10 +1284,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1294,10 +1298,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>4000001</v>
+        <v>30001</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -1308,38 +1312,38 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>6000001</v>
+        <v>5000001</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>6010001</v>
+        <v>6000001</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
@@ -1350,24 +1354,24 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>7000001</v>
+        <v>6010001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>7010001</v>
+        <v>7000001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
@@ -1378,24 +1382,24 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>8000001</v>
+        <v>7010001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>8010001</v>
+        <v>8000001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1406,24 +1410,24 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>9000001</v>
+        <v>8010001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>10010001</v>
+        <v>9000001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>10020001</v>
+        <v>10010001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1448,10 +1452,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>11010001</v>
+        <v>10020001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1462,10 +1466,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>54010001</v>
+        <v>11010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1476,10 +1480,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>54030001</v>
+        <v>54010001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1490,10 +1494,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1504,10 +1508,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1518,10 +1522,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1532,10 +1536,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1546,10 +1550,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1560,10 +1564,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1574,10 +1578,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1588,10 +1592,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1602,10 +1606,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1616,10 +1620,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1630,10 +1634,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1644,10 +1648,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>55010001</v>
+        <v>54250001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1658,10 +1662,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>55020001</v>
+        <v>55010001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1672,10 +1676,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>55030001</v>
+        <v>55020001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1686,10 +1690,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>55040001</v>
+        <v>55030001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1700,10 +1704,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>55050001</v>
+        <v>55040001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1714,10 +1718,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>55060001</v>
+        <v>55050001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1728,10 +1732,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>55070001</v>
+        <v>55060001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1742,10 +1746,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>56010001</v>
+        <v>55070001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1756,10 +1760,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>56040001</v>
+        <v>56010001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1770,10 +1774,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1784,10 +1788,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1798,10 +1802,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1812,10 +1816,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>57010001</v>
+        <v>56100001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1826,10 +1830,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>57040001</v>
+        <v>57010001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1840,10 +1844,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1854,10 +1858,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1868,10 +1872,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1882,10 +1886,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1896,10 +1900,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>58010001</v>
+        <v>57120001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1910,10 +1914,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>58040001</v>
+        <v>58010001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1924,10 +1928,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1938,10 +1942,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1952,10 +1956,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1966,10 +1970,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>59010001</v>
+        <v>58110001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1980,10 +1984,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -1994,10 +1998,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2008,10 +2012,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2022,10 +2026,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2036,10 +2040,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2050,10 +2054,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2064,10 +2068,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2078,10 +2082,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2092,10 +2096,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2106,10 +2110,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2120,10 +2124,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>60010001</v>
+        <v>59220001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2134,10 +2138,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2148,10 +2152,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2162,10 +2166,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2176,10 +2180,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2190,10 +2194,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>61020001</v>
+        <v>60110001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2204,10 +2208,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2218,10 +2222,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2232,10 +2236,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2246,10 +2250,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2260,10 +2264,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2274,10 +2278,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2288,10 +2292,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2302,22 +2306,36 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
         <v>61180001</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B106" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C105" s="2">
-        <v>0</v>
-      </c>
-      <c r="D105" s="2">
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D83" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D30">
-    <sortCondition ref="A25:A30"/>
+  <autoFilter ref="A4:D84" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:D31">
+    <sortCondition ref="A26:A31"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70EC847A-03AF-4614-A71A-6FA9AC87AF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CC3F7C-8B21-41AB-AE12-DB245091452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="132">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -448,6 +448,14 @@
   </si>
   <si>
     <t>冰弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101011,100101021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100301011,100301021</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -906,7 +914,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>955001008</v>
+        <v>95100101</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -920,7 +928,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>955001004</v>
+        <v>95200101</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -934,7 +942,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>955001006</v>
+        <v>95000101</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>129</v>
@@ -1206,7 +1214,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
@@ -1262,7 +1270,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D30" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20CC3F7C-8B21-41AB-AE12-DB245091452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604CCD4A-60FE-4D0F-BA5F-1B3EED0FD200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$89</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="142">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,257 +205,298 @@
     <t>boss_03-普攻</t>
   </si>
   <si>
+    <t>陨石</t>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+  </si>
+  <si>
+    <t>闪电链</t>
+  </si>
+  <si>
+    <t>电磁爆炸</t>
+  </si>
+  <si>
+    <t>中毒传染</t>
+  </si>
+  <si>
+    <t>瘟疫传染</t>
+  </si>
+  <si>
+    <t>复活</t>
+  </si>
+  <si>
+    <t>生命药剂</t>
+  </si>
+  <si>
+    <t>击中回血</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>旋风斩</t>
+  </si>
+  <si>
+    <t>半月斩</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>攻击速度提高</t>
+  </si>
+  <si>
+    <t>攻击提高</t>
+  </si>
+  <si>
+    <t>防御提高</t>
+  </si>
+  <si>
+    <t>生命提高</t>
+  </si>
+  <si>
+    <t>击中回血效果提高</t>
+  </si>
+  <si>
+    <t>暴击几率提高</t>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+  </si>
+  <si>
+    <t>伤害提高</t>
+  </si>
+  <si>
+    <t>受到伤害提高</t>
+  </si>
+  <si>
+    <t>持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>攻击几率使目标冰冻</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星触发释放冰霜新星</t>
+  </si>
+  <si>
+    <t>使冰冻目标再次冰冻时触发额外伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时造成额外伤害</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星必定使目标冰冻</t>
+  </si>
+  <si>
+    <t>攻击几率使目标燃烧</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放陨石</t>
+  </si>
+  <si>
+    <t>燃烧造成的伤害提高</t>
+  </si>
+  <si>
+    <t>陨石必定使目标燃烧</t>
+  </si>
+  <si>
+    <t>击杀燃烧怪物时触发释放死亡爆炸</t>
+  </si>
+  <si>
+    <t>攻击几率使目标触电</t>
+  </si>
+  <si>
+    <t>闪电链可弹射</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放闪电链</t>
+  </si>
+  <si>
+    <t>提高触电时受到攻击造成的额外伤害</t>
+  </si>
+  <si>
+    <t>造成触电时立刻触发触电伤害</t>
+  </si>
+  <si>
+    <t>击杀触电怪时触发释放电磁爆炸</t>
+  </si>
+  <si>
+    <t>攻击几率使目标中毒</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放传染</t>
+  </si>
+  <si>
+    <t>使中毒目标再次中毒时造成额外伤害</t>
+  </si>
+  <si>
+    <t>击杀中毒怪物时触发释放瘟疫</t>
+  </si>
+  <si>
+    <t>使目标获得瘟疫状态</t>
+  </si>
+  <si>
+    <t>每损失指定比例血量触发获得护盾</t>
+  </si>
+  <si>
+    <t>护盾值-根据自身生命最大值比例</t>
+  </si>
+  <si>
+    <t>拥有护盾时同时有受伤降低效果</t>
+  </si>
+  <si>
+    <t>击杀怪物触发击杀回血效果</t>
+  </si>
+  <si>
+    <t>击杀回血-回复量根据击中回血数值倍率</t>
+  </si>
+  <si>
+    <t>满血触发效果</t>
+  </si>
+  <si>
+    <t>低血时同时有受到伤害降低效果</t>
+  </si>
+  <si>
+    <t>死亡时触发释放复活</t>
+  </si>
+  <si>
+    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放多重打击</t>
+  </si>
+  <si>
+    <t>提高多重打击的额外伤害</t>
+  </si>
+  <si>
+    <t>攻击次数触发释放旋风斩</t>
+  </si>
+  <si>
+    <t>释放旋风斩触发释放半月斩</t>
+  </si>
+  <si>
+    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+  </si>
+  <si>
+    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+  </si>
+  <si>
+    <t>致命暴击状态触发技能攻击速度提高</t>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+  </si>
+  <si>
+    <t>斩杀时暴击触发斩杀血线变化</t>
+  </si>
+  <si>
+    <t>斩杀血线的值增加</t>
+  </si>
+  <si>
+    <t>玩家1档普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家2档普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家3普攻-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物韧性被打空对自己释放易伤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100201011,100201021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100101011,100101021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100301011,100301021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>boss_05-普攻</t>
-  </si>
-  <si>
-    <t>陨石</t>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-  </si>
-  <si>
-    <t>闪电链</t>
-  </si>
-  <si>
-    <t>电磁爆炸</t>
-  </si>
-  <si>
-    <t>中毒传染</t>
-  </si>
-  <si>
-    <t>瘟疫传染</t>
-  </si>
-  <si>
-    <t>复活</t>
-  </si>
-  <si>
-    <t>生命药剂</t>
-  </si>
-  <si>
-    <t>击中回血</t>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-  </si>
-  <si>
-    <t>旋风斩</t>
-  </si>
-  <si>
-    <t>半月斩</t>
-  </si>
-  <si>
-    <t>重击</t>
-  </si>
-  <si>
-    <t>攻击速度提高</t>
-  </si>
-  <si>
-    <t>攻击提高</t>
-  </si>
-  <si>
-    <t>防御提高</t>
-  </si>
-  <si>
-    <t>生命提高</t>
-  </si>
-  <si>
-    <t>击中回血效果提高</t>
-  </si>
-  <si>
-    <t>暴击几率提高</t>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-  </si>
-  <si>
-    <t>伤害提高</t>
-  </si>
-  <si>
-    <t>受到伤害提高</t>
-  </si>
-  <si>
-    <t>持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>攻击几率使目标冰冻</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星触发释放冰霜新星</t>
-  </si>
-  <si>
-    <t>使冰冻目标再次冰冻时触发额外伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时造成额外伤害</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星必定使目标冰冻</t>
-  </si>
-  <si>
-    <t>攻击几率使目标燃烧</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放陨石</t>
-  </si>
-  <si>
-    <t>燃烧造成的伤害提高</t>
-  </si>
-  <si>
-    <t>陨石必定使目标燃烧</t>
-  </si>
-  <si>
-    <t>击杀燃烧怪物时触发释放死亡爆炸</t>
-  </si>
-  <si>
-    <t>攻击几率使目标触电</t>
-  </si>
-  <si>
-    <t>闪电链可弹射</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放闪电链</t>
-  </si>
-  <si>
-    <t>提高触电时受到攻击造成的额外伤害</t>
-  </si>
-  <si>
-    <t>造成触电时立刻触发触电伤害</t>
-  </si>
-  <si>
-    <t>击杀触电怪时触发释放电磁爆炸</t>
-  </si>
-  <si>
-    <t>攻击几率使目标中毒</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放传染</t>
-  </si>
-  <si>
-    <t>使中毒目标再次中毒时造成额外伤害</t>
-  </si>
-  <si>
-    <t>击杀中毒怪物时触发释放瘟疫</t>
-  </si>
-  <si>
-    <t>使目标获得瘟疫状态</t>
-  </si>
-  <si>
-    <t>每损失指定比例血量触发获得护盾</t>
-  </si>
-  <si>
-    <t>护盾值-根据自身生命最大值比例</t>
-  </si>
-  <si>
-    <t>拥有护盾时同时有受伤降低效果</t>
-  </si>
-  <si>
-    <t>击杀怪物触发击杀回血效果</t>
-  </si>
-  <si>
-    <t>击杀回血-回复量根据击中回血数值倍率</t>
-  </si>
-  <si>
-    <t>满血触发效果</t>
-  </si>
-  <si>
-    <t>低血时同时有受到伤害降低效果</t>
-  </si>
-  <si>
-    <t>死亡时触发释放复活</t>
-  </si>
-  <si>
-    <t>复活时回复血郞、触发间隔、每轮挑战最大次数</t>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放多重打击</t>
-  </si>
-  <si>
-    <t>提高多重打击的额外伤害</t>
-  </si>
-  <si>
-    <t>攻击次数触发释放旋风斩</t>
-  </si>
-  <si>
-    <t>释放旋风斩触发释放半月斩</t>
-  </si>
-  <si>
-    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-  </si>
-  <si>
-    <t>暴击触发技能：暴击伤害提高、重击需要的攻击次数累计值+1，致命暴击状态</t>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-  </si>
-  <si>
-    <t>致命暴击状态触发技能攻击速度提高</t>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-  </si>
-  <si>
-    <t>斩杀时暴击触发斩杀血线变化</t>
-  </si>
-  <si>
-    <t>斩杀血线的值增加</t>
-  </si>
-  <si>
-    <t>玩家1档普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家2档普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家3普攻-2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物韧性被打空对自己释放易伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100201011,100201021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰弹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100101011,100101021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100301011,100301021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级1-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级2-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级4远程-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蜘蛛怪等级1-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2精英-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001011,1001021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002011,1002021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004011,1004021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14001011,14001021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002011,3002021</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -463,7 +504,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,6 +545,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -561,7 +610,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -572,6 +621,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -853,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -945,7 +997,7 @@
         <v>95000101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -1183,7 +1235,7 @@
         <v>20160001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>34</v>
@@ -1197,7 +1249,7 @@
         <v>25010001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="1">
         <v>0</v>
@@ -1207,84 +1259,84 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="A26" s="1">
+        <v>201001011</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
-      </c>
-      <c r="D27" s="2">
+      <c r="A27" s="1">
+        <v>201002011</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>10201</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="A28" s="1">
+        <v>201004011</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>10202</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="A29" s="1">
+        <v>214001011</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>10301</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="A30" s="1">
+        <v>203002011</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>10302</v>
+        <v>10101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1292,10 +1344,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>20001</v>
+        <v>10102</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
@@ -1306,13 +1358,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>30001</v>
+        <v>10201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="2">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1320,10 +1372,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>4000001</v>
+        <v>10202</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
@@ -1334,178 +1386,178 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>5000001</v>
+        <v>10301</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="D35" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>6000001</v>
+        <v>10302</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>31000020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>6010001</v>
+        <v>20001</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>31000020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>7000001</v>
+        <v>30001</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>31000040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>7010001</v>
+        <v>4000001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>31000040</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>8000001</v>
+        <v>5000001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>31000030</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>8010001</v>
+        <v>6000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>31000030</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>9000001</v>
+        <v>6010001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>0</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>10010001</v>
+        <v>7000001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>0</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>10020001</v>
+        <v>7010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>11010001</v>
+        <v>8000001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>54010001</v>
+        <v>8010001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>54030001</v>
+        <v>9000001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1516,10 +1568,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>54050001</v>
+        <v>10010001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1530,10 +1582,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>54070001</v>
+        <v>10020001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1544,10 +1596,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>54090001</v>
+        <v>11010001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1558,10 +1610,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54110001</v>
+        <v>54010001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1572,10 +1624,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54130001</v>
+        <v>54030001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1586,10 +1638,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54150001</v>
+        <v>54050001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1600,10 +1652,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54170001</v>
+        <v>54070001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1614,10 +1666,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54190001</v>
+        <v>54090001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1628,10 +1680,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54210001</v>
+        <v>54110001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1642,10 +1694,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54230001</v>
+        <v>54130001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1656,10 +1708,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>54250001</v>
+        <v>54150001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1670,10 +1722,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>55010001</v>
+        <v>54170001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1684,10 +1736,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>55020001</v>
+        <v>54190001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1698,10 +1750,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>55030001</v>
+        <v>54210001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1712,10 +1764,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>55040001</v>
+        <v>54230001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1726,10 +1778,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>55050001</v>
+        <v>54250001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1740,10 +1792,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>55060001</v>
+        <v>55010001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1754,10 +1806,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>55070001</v>
+        <v>55020001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1768,10 +1820,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>56010001</v>
+        <v>55030001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1782,10 +1834,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>56040001</v>
+        <v>55040001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1796,10 +1848,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>56060001</v>
+        <v>55050001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1810,10 +1862,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>56080001</v>
+        <v>55060001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1824,10 +1876,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>56100001</v>
+        <v>55070001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1838,10 +1890,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>57010001</v>
+        <v>56010001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1852,10 +1904,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>57040001</v>
+        <v>56040001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1866,10 +1918,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>57060001</v>
+        <v>56060001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1880,10 +1932,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>57080001</v>
+        <v>56080001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1894,10 +1946,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>57100001</v>
+        <v>56100001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1908,10 +1960,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>57120001</v>
+        <v>57010001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1922,10 +1974,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>58010001</v>
+        <v>57040001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1936,10 +1988,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>58040001</v>
+        <v>57060001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1950,10 +2002,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>58060001</v>
+        <v>57080001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1964,10 +2016,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>58080001</v>
+        <v>57100001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -1978,10 +2030,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>58110001</v>
+        <v>57120001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -1992,10 +2044,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>59010001</v>
+        <v>58010001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2006,10 +2058,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>59030001</v>
+        <v>58040001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2020,10 +2072,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>59050001</v>
+        <v>58060001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2034,10 +2086,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>59070001</v>
+        <v>58080001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2048,10 +2100,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>59090001</v>
+        <v>58110001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2062,10 +2114,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59110001</v>
+        <v>59010001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2076,10 +2128,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59130001</v>
+        <v>59030001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2090,10 +2142,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59150001</v>
+        <v>59050001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2104,10 +2156,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59180001</v>
+        <v>59070001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2118,10 +2170,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59200001</v>
+        <v>59090001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2132,10 +2184,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>59220001</v>
+        <v>59110001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2146,10 +2198,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>60010001</v>
+        <v>59130001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2160,10 +2212,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>60030001</v>
+        <v>59150001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2174,10 +2226,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>60060001</v>
+        <v>59180001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2188,10 +2240,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>60090001</v>
+        <v>59200001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2202,10 +2254,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>60110001</v>
+        <v>59220001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2216,10 +2268,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>61020001</v>
+        <v>60010001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2230,10 +2282,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>61040001</v>
+        <v>60030001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2244,10 +2296,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>61060001</v>
+        <v>60060001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2258,10 +2310,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>61080001</v>
+        <v>60090001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2272,10 +2324,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>61100001</v>
+        <v>60110001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2286,10 +2338,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61120001</v>
+        <v>61020001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2300,10 +2352,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>61140001</v>
+        <v>61040001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2314,10 +2366,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>61160001</v>
+        <v>61060001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>
@@ -2328,22 +2380,92 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
+        <v>61080001</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>61100001</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>61120001</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>61140001</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
         <v>61180001</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C106" s="2">
-        <v>0</v>
-      </c>
-      <c r="D106" s="2">
+      <c r="B111" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D84" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:D31">
-    <sortCondition ref="A26:A31"/>
+  <autoFilter ref="A4:D89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D36">
+    <sortCondition ref="A31:A36"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604CCD4A-60FE-4D0F-BA5F-1B3EED0FD200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3173971D-AF10-4D40-BABA-40C9611430C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,22 +440,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>100201011,100201021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>冰弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>100101011,100101021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100301011,100301021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>boss_05-普攻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -498,6 +486,27 @@
   <si>
     <t>3002011,3002021</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11101,11102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11201,11202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12101,12102,12103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12201,12202,12203</t>
+  </si>
+  <si>
+    <t>13101,13102,13103</t>
+  </si>
+  <si>
+    <t>13201,13202,13203</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1006,7 @@
         <v>95000101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -1235,7 +1244,7 @@
         <v>20160001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>34</v>
@@ -1263,10 +1272,10 @@
         <v>201001011</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1277,10 +1286,10 @@
         <v>201002011</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1291,10 +1300,10 @@
         <v>201004011</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1305,10 +1314,10 @@
         <v>214001011</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1319,10 +1328,10 @@
         <v>203002011</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -1336,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1349,8 +1358,8 @@
       <c r="B32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="2">
-        <v>0</v>
+      <c r="C32" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1364,7 +1373,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1377,8 +1386,8 @@
       <c r="B34" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C34" s="2">
-        <v>0</v>
+      <c r="C34" s="5" t="s">
+        <v>142</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1392,7 +1401,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1405,8 +1414,8 @@
       <c r="B36" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C36" s="2">
-        <v>0</v>
+      <c r="C36" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3173971D-AF10-4D40-BABA-40C9611430C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3796F8-120A-4E06-A64D-119B52A5C2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,21 +492,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11201,11202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>12101,12102,12103</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>12201,12202,12203</t>
-  </si>
-  <si>
-    <t>13101,13102,13103</t>
-  </si>
-  <si>
-    <t>13201,13202,13203</t>
+    <t>11201,11202,11203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12201,12202,12203,12204,12205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -919,7 +922,7 @@
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.625" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="24.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1359,7 +1362,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1373,7 +1376,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3796F8-120A-4E06-A64D-119B52A5C2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35966767-7A26-463F-A99A-5C1927BE1554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -493,10 +493,6 @@
   </si>
   <si>
     <t>12101,12102,12103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11201,11202,11203</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1362,7 +1358,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1390,7 +1386,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1404,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1418,7 +1414,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35966767-7A26-463F-A99A-5C1927BE1554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3C77-E576-4206-8521-840EA243B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,11 +500,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>13101</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13201</t>
+    <t>13101,13102,13103,13104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13201,13202,13203,13204,13205,13206</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +918,7 @@
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.625" customWidth="1"/>
-    <col min="3" max="3" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3C77-E576-4206-8521-840EA243B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F79BA6-5FB8-4C76-8649-807491B96F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,24 +488,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11101,11102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12101,12102,12103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12201,12202,12203,12204,12205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13101,13102,13103,13104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13201,13202,13203,13204,13205,13206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>21101,21102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21201,21202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22101,22102,22103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22201,22202,22203,22204,22205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23101,23102,23103,23104</t>
+  </si>
+  <si>
+    <t>23201,23202,23203,23204,23205,23206</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1360,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1372,7 +1374,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1386,7 +1388,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1400,7 +1402,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1414,7 +1416,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F79BA6-5FB8-4C76-8649-807491B96F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3C77-E576-4206-8521-840EA243B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,26 +488,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>21101,21102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21201,21202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>22101,22102,22103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>22201,22202,22203,22204,22205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23101,23102,23103,23104</t>
-  </si>
-  <si>
-    <t>23201,23202,23203,23204,23205,23206</t>
+    <t>11101,11102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12101,12102,12103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12201,12202,12203,12204,12205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13101,13102,13103,13104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13201,13202,13203,13204,13205,13206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1360,7 +1358,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1374,7 +1372,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1388,7 +1386,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1402,7 +1400,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1416,7 +1414,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F79BA6-5FB8-4C76-8649-807491B96F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F95A58-B484-49C9-88C5-D4AEF2EB25D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,14 +488,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>21101,21102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>21201,21202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>22101,22102,22103</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -508,6 +500,10 @@
   </si>
   <si>
     <t>23201,23202,23203,23204,23205,23206</t>
+  </si>
+  <si>
+    <t>21301,21302,21303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1346,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1360,7 +1356,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1374,7 +1370,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1388,7 +1384,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1402,7 +1398,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1416,7 +1412,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998A3C77-E576-4206-8521-840EA243B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F95A58-B484-49C9-88C5-D4AEF2EB25D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -488,23 +488,21 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11101,11102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12101,12102,12103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12201,12202,12203,12204,12205</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13101,13102,13103,13104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13201,13202,13203,13204,13205,13206</t>
+    <t>22101,22102,22103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22201,22202,22203,22204,22205</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23101,23102,23103,23104</t>
+  </si>
+  <si>
+    <t>23201,23202,23203,23204,23205,23206</t>
+  </si>
+  <si>
+    <t>21301,21302,21303</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1344,7 +1342,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1358,7 +1356,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1372,7 +1370,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1386,7 +1384,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1400,7 +1398,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1414,7 +1412,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F95A58-B484-49C9-88C5-D4AEF2EB25D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF5AF1-5173-447B-86A1-E19204843AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,10 +488,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>22101,22102,22103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>22201,22202,22203,22204,22205</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -502,7 +498,7 @@
     <t>23201,23202,23203,23204,23205,23206</t>
   </si>
   <si>
-    <t>21301,21302,21303</t>
+    <t>21101,21102,21103</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1342,7 +1338,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1356,7 +1352,7 @@
         <v>123</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1370,7 +1366,7 @@
         <v>11</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1384,7 +1380,7 @@
         <v>124</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1398,7 +1394,7 @@
         <v>12</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1412,7 +1408,7 @@
         <v>125</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CF5AF1-5173-447B-86A1-E19204843AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023F189D-B4E6-40DD-A2BB-624D8E31E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -499,6 +499,20 @@
   </si>
   <si>
     <t>21101,21102,21103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺</t>
+  </si>
+  <si>
+    <t>升龙击</t>
+  </si>
+  <si>
+    <t>22101,22102,22103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23101,23102,23103,23104</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -612,7 +626,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -625,6 +639,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -907,7 +924,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D113"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1024,13 +1041,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>20010001</v>
+        <v>20021</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="1">
-        <v>990102</v>
+        <v>143</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1038,13 +1055,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>20020001</v>
+        <v>20022</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>144</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>146</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -1052,13 +1069,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>20030001</v>
+        <v>20010001</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
+      </c>
+      <c r="C11" s="1">
+        <v>990102</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1066,13 +1083,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>20040001</v>
+        <v>20020001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1080,13 +1097,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>20050001</v>
+        <v>20030001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1094,13 +1111,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>20060001</v>
+        <v>20040001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1108,13 +1125,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>20070001</v>
+        <v>20050001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1122,13 +1139,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>20080001</v>
+        <v>20060001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1136,13 +1153,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>20090001</v>
+        <v>20070001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1150,13 +1167,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>20100001</v>
+        <v>20080001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1164,13 +1181,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>20110001</v>
+        <v>20090001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1178,13 +1195,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>20120001</v>
+        <v>20100001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1192,13 +1209,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20130001</v>
+        <v>20110001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1206,13 +1223,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>20140001</v>
+        <v>20120001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1220,13 +1237,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>20150001</v>
+        <v>20130001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1234,13 +1251,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>20160001</v>
+        <v>20140001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1248,13 +1265,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>25010001</v>
+        <v>20150001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1262,13 +1279,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>201001011</v>
+        <v>20160001</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>134</v>
+        <v>128</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1276,13 +1293,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>201002011</v>
+        <v>25010001</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>135</v>
+        <v>126</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1290,13 +1307,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>201004011</v>
+        <v>201001011</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1304,13 +1321,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>214001011</v>
+        <v>201002011</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1318,52 +1335,52 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
+        <v>201004011</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>214001011</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>203002011</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="D32" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>142</v>
@@ -1374,13 +1391,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10202</v>
+        <v>10102</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1388,13 +1405,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1402,13 +1419,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10302</v>
+        <v>10202</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -1416,13 +1433,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>20001</v>
+        <v>10301</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="2">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1430,13 +1447,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>30001</v>
+        <v>10302</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="2">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1444,10 +1461,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>4000001</v>
+        <v>20001</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1458,136 +1475,136 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>5000001</v>
+        <v>30001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>6000001</v>
+        <v>4000001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>31000020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>6010001</v>
+        <v>5000001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>7000001</v>
+        <v>6000001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>7010001</v>
+        <v>6010001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>8000001</v>
+        <v>7000001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>8010001</v>
+        <v>7010001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>9000001</v>
+        <v>8000001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
       </c>
       <c r="D47" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>10010001</v>
+        <v>8010001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>10020001</v>
+        <v>9000001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1598,10 +1615,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>11010001</v>
+        <v>10010001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1612,10 +1629,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>54010001</v>
+        <v>10020001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1626,10 +1643,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>54030001</v>
+        <v>11010001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1640,10 +1657,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54050001</v>
+        <v>54010001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1654,10 +1671,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54070001</v>
+        <v>54030001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1668,10 +1685,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54090001</v>
+        <v>54050001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1682,10 +1699,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54110001</v>
+        <v>54070001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1696,10 +1713,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54130001</v>
+        <v>54090001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1710,10 +1727,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>54150001</v>
+        <v>54110001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1724,10 +1741,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>54170001</v>
+        <v>54130001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1738,10 +1755,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>54190001</v>
+        <v>54150001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1752,10 +1769,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>54210001</v>
+        <v>54170001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1766,10 +1783,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>54230001</v>
+        <v>54190001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1780,10 +1797,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>54250001</v>
+        <v>54210001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1794,10 +1811,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>55010001</v>
+        <v>54230001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1808,10 +1825,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>55020001</v>
+        <v>54250001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1822,10 +1839,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>55030001</v>
+        <v>55010001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1836,10 +1853,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>55040001</v>
+        <v>55020001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1850,10 +1867,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>55050001</v>
+        <v>55030001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1864,10 +1881,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>55060001</v>
+        <v>55040001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1878,10 +1895,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>55070001</v>
+        <v>55050001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1892,10 +1909,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>56010001</v>
+        <v>55060001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1906,10 +1923,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>56040001</v>
+        <v>55070001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1920,10 +1937,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>56060001</v>
+        <v>56010001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1934,10 +1951,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>56080001</v>
+        <v>56040001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1948,10 +1965,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>56100001</v>
+        <v>56060001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1962,10 +1979,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>57010001</v>
+        <v>56080001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1976,10 +1993,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>57040001</v>
+        <v>56100001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -1990,10 +2007,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>57060001</v>
+        <v>57010001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -2004,10 +2021,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>57080001</v>
+        <v>57040001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -2018,10 +2035,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>57100001</v>
+        <v>57060001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -2032,10 +2049,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>57120001</v>
+        <v>57080001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -2046,10 +2063,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>58010001</v>
+        <v>57100001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2060,10 +2077,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>58040001</v>
+        <v>57120001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2074,10 +2091,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>58060001</v>
+        <v>58010001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2088,10 +2105,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>58080001</v>
+        <v>58040001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2102,10 +2119,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>58110001</v>
+        <v>58060001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2116,10 +2133,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>59010001</v>
+        <v>58080001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2130,10 +2147,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>59030001</v>
+        <v>58110001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2144,10 +2161,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59050001</v>
+        <v>59010001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2158,10 +2175,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59070001</v>
+        <v>59030001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2172,10 +2189,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59090001</v>
+        <v>59050001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2186,10 +2203,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>59110001</v>
+        <v>59070001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2200,10 +2217,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>59130001</v>
+        <v>59090001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2214,10 +2231,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>59150001</v>
+        <v>59110001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2228,10 +2245,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>59180001</v>
+        <v>59130001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2242,10 +2259,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>59200001</v>
+        <v>59150001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2256,10 +2273,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>59220001</v>
+        <v>59180001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2270,10 +2287,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>60010001</v>
+        <v>59200001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2284,10 +2301,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>60030001</v>
+        <v>59220001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2298,10 +2315,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>60060001</v>
+        <v>60010001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2312,10 +2329,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>60090001</v>
+        <v>60030001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2326,10 +2343,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>60110001</v>
+        <v>60060001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2340,10 +2357,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>61020001</v>
+        <v>60090001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2354,10 +2371,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>61040001</v>
+        <v>60110001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2368,10 +2385,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>61060001</v>
+        <v>61020001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>
@@ -2382,10 +2399,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>61080001</v>
+        <v>61040001</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -2396,10 +2413,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>61100001</v>
+        <v>61060001</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -2410,10 +2427,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>61120001</v>
+        <v>61080001</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -2424,10 +2441,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>61140001</v>
+        <v>61100001</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
@@ -2438,10 +2455,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>61160001</v>
+        <v>61120001</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -2452,22 +2469,50 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
+        <v>61140001</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
         <v>61180001</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B113" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C111" s="2">
-        <v>0</v>
-      </c>
-      <c r="D111" s="2">
+      <c r="C113" s="2">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D89" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D36">
-    <sortCondition ref="A31:A36"/>
+  <autoFilter ref="A4:D91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:D38">
+    <sortCondition ref="A33:A38"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023F189D-B4E6-40DD-A2BB-624D8E31E45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A545F497-5F3F-47E3-BEAB-F97287E8623A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="149">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -508,11 +508,19 @@
     <t>升龙击</t>
   </si>
   <si>
-    <t>22101,22102,22103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>23101,23102,23103,23104</t>
+    <t>22102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆炎冲刺追加砸地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -924,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1047,7 +1055,7 @@
         <v>143</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1061,7 +1069,7 @@
         <v>144</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -1069,13 +1077,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>20010001</v>
+        <v>20023</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="1">
-        <v>990102</v>
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>147</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1083,13 +1091,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>20020001</v>
+        <v>20010001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="C12" s="1">
+        <v>990102</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -1097,13 +1105,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>20030001</v>
+        <v>20020001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -1111,13 +1119,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>20040001</v>
+        <v>20030001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -1125,13 +1133,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>20050001</v>
+        <v>20040001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -1139,13 +1147,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>20060001</v>
+        <v>20050001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1153,13 +1161,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>20070001</v>
+        <v>20060001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1167,13 +1175,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>20080001</v>
+        <v>20070001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1181,13 +1189,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>20090001</v>
+        <v>20080001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1195,13 +1203,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>20100001</v>
+        <v>20090001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1209,13 +1217,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20110001</v>
+        <v>20100001</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1223,13 +1231,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>20120001</v>
+        <v>20110001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1237,13 +1245,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>20130001</v>
+        <v>20120001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1251,13 +1259,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>20140001</v>
+        <v>20130001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1265,13 +1273,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>20150001</v>
+        <v>20140001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1279,13 +1287,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>20160001</v>
+        <v>20150001</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1293,13 +1301,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>25010001</v>
+        <v>20160001</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
+        <v>128</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1307,13 +1315,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>201001011</v>
+        <v>25010001</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>134</v>
+        <v>126</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1321,13 +1329,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>201002011</v>
+        <v>201001011</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1335,13 +1343,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>201004011</v>
+        <v>201002011</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -1349,13 +1357,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>214001011</v>
+        <v>201004011</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -1363,38 +1371,38 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
+        <v>214001011</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>203002011</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C33" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="D33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>142</v>
@@ -1405,10 +1413,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>142</v>
@@ -1419,13 +1427,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -1433,13 +1441,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1447,13 +1455,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1461,13 +1469,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>20001</v>
+        <v>10302</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1475,10 +1483,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C40" s="2">
         <v>0</v>
@@ -1489,10 +1497,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>4000001</v>
+        <v>30001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1503,38 +1511,38 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
       </c>
       <c r="D42" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>6000001</v>
+        <v>5000001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>6010001</v>
+        <v>6000001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -1545,24 +1553,24 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>7000001</v>
+        <v>6010001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>7010001</v>
+        <v>7000001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
@@ -1573,24 +1581,24 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>8000001</v>
+        <v>7010001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
       </c>
       <c r="D47" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>8010001</v>
+        <v>8000001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1601,24 +1609,24 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>9000001</v>
+        <v>8010001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>10010001</v>
+        <v>9000001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
@@ -1629,10 +1637,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>10020001</v>
+        <v>10010001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1643,10 +1651,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>11010001</v>
+        <v>10020001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1657,10 +1665,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>54010001</v>
+        <v>11010001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1671,10 +1679,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54030001</v>
+        <v>54010001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1685,10 +1693,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1699,10 +1707,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1713,10 +1721,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1727,10 +1735,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1741,10 +1749,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1755,10 +1763,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1769,10 +1777,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1783,10 +1791,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1797,10 +1805,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1811,10 +1819,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1825,10 +1833,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1839,10 +1847,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>55010001</v>
+        <v>54250001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1853,10 +1861,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>55020001</v>
+        <v>55010001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1867,10 +1875,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>55030001</v>
+        <v>55020001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1881,10 +1889,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>55040001</v>
+        <v>55030001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1895,10 +1903,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>55050001</v>
+        <v>55040001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1909,10 +1917,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>55060001</v>
+        <v>55050001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1923,10 +1931,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>55070001</v>
+        <v>55060001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1937,10 +1945,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>56010001</v>
+        <v>55070001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1951,10 +1959,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>56040001</v>
+        <v>56010001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1965,10 +1973,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1979,10 +1987,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -1993,10 +2001,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -2007,10 +2015,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>57010001</v>
+        <v>56100001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -2021,10 +2029,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>57040001</v>
+        <v>57010001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -2035,10 +2043,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -2049,10 +2057,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -2063,10 +2071,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2077,10 +2085,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2091,10 +2099,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>58010001</v>
+        <v>57120001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2105,10 +2113,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>58040001</v>
+        <v>58010001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2119,10 +2127,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2133,10 +2141,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2147,10 +2155,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2161,10 +2169,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>59010001</v>
+        <v>58110001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2175,10 +2183,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2189,10 +2197,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2203,10 +2211,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2217,10 +2225,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2231,10 +2239,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2245,10 +2253,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2259,10 +2267,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2273,10 +2281,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2287,10 +2295,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2301,10 +2309,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2315,10 +2323,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>60010001</v>
+        <v>59220001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2329,10 +2337,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2343,10 +2351,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2357,10 +2365,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2371,10 +2379,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2385,10 +2393,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>61020001</v>
+        <v>60110001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>
@@ -2399,10 +2407,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -2413,10 +2421,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -2427,10 +2435,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -2441,10 +2449,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -2469,10 +2477,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C111" s="2">
         <v>0</v>
@@ -2483,10 +2491,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C112" s="2">
         <v>0</v>
@@ -2497,22 +2505,36 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
         <v>61180001</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B114" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C113" s="2">
-        <v>0</v>
-      </c>
-      <c r="D113" s="2">
+      <c r="C114" s="2">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D91" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:D38">
-    <sortCondition ref="A33:A38"/>
+  <autoFilter ref="A4:D92" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D39">
+    <sortCondition ref="A34:A39"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A545F497-5F3F-47E3-BEAB-F97287E8623A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583E4A20-58CD-4F70-B6DD-11808E6E8C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="151">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -464,10 +464,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>僵尸等级2精英-普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1001011,1001021</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -521,6 +517,18 @@
   </si>
   <si>
     <t>爆炎冲刺追加砸地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僵尸等级2-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石像鬼精英-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16001001,16001002,16001003</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -932,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1052,10 +1060,10 @@
         <v>20021</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1066,10 +1074,10 @@
         <v>20022</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -1080,10 +1088,10 @@
         <v>20023</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1335,7 +1343,7 @@
         <v>129</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1349,7 +1357,7 @@
         <v>130</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -1363,7 +1371,7 @@
         <v>131</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -1377,7 +1385,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -1388,38 +1396,38 @@
         <v>203002011</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="A34" s="1">
+        <v>203002011</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1427,13 +1435,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -1441,13 +1449,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1455,13 +1463,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1469,13 +1477,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>10302</v>
+        <v>10301</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1483,13 +1491,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>20001</v>
+        <v>10302</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2">
-        <v>0</v>
+        <v>125</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -1497,10 +1505,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>30001</v>
+        <v>20001</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1511,10 +1519,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>4000001</v>
+        <v>30001</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1525,38 +1533,38 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>5000001</v>
+        <v>4000001</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>31000010</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>6000001</v>
+        <v>5000001</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>31000020</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>6010001</v>
+        <v>6000001</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1567,24 +1575,24 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>7000001</v>
+        <v>6010001</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="2">
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>31000040</v>
+        <v>31000020</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>7010001</v>
+        <v>7000001</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
@@ -1595,24 +1603,24 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>8000001</v>
+        <v>7010001</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>31000030</v>
+        <v>31000040</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>8010001</v>
+        <v>8000001</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1623,24 +1631,24 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>9000001</v>
+        <v>8010001</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>0</v>
+        <v>31000030</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>10010001</v>
+        <v>9000001</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1651,10 +1659,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>10020001</v>
+        <v>10010001</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="2">
         <v>0</v>
@@ -1665,10 +1673,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>11010001</v>
+        <v>10020001</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1679,10 +1687,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>54010001</v>
+        <v>11010001</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1693,10 +1701,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>54030001</v>
+        <v>54010001</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="2">
         <v>0</v>
@@ -1707,10 +1715,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" s="2">
         <v>0</v>
@@ -1721,10 +1729,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" s="2">
         <v>0</v>
@@ -1735,10 +1743,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" s="2">
         <v>0</v>
@@ -1749,10 +1757,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1763,10 +1771,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1777,10 +1785,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
@@ -1791,10 +1799,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62" s="2">
         <v>0</v>
@@ -1805,10 +1813,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>0</v>
@@ -1819,10 +1827,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
@@ -1833,10 +1841,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1847,10 +1855,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C66" s="2">
         <v>0</v>
@@ -1861,10 +1869,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>55010001</v>
+        <v>54250001</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C67" s="2">
         <v>0</v>
@@ -1875,10 +1883,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>55020001</v>
+        <v>55010001</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1889,10 +1897,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>55030001</v>
+        <v>55020001</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C69" s="2">
         <v>0</v>
@@ -1903,10 +1911,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>55040001</v>
+        <v>55030001</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1917,10 +1925,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>55050001</v>
+        <v>55040001</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1931,10 +1939,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>55060001</v>
+        <v>55050001</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1945,10 +1953,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>55070001</v>
+        <v>55060001</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C73" s="2">
         <v>0</v>
@@ -1959,10 +1967,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>56010001</v>
+        <v>55070001</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -1973,10 +1981,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>56040001</v>
+        <v>56010001</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
@@ -1987,10 +1995,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C76" s="2">
         <v>0</v>
@@ -2001,10 +2009,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
@@ -2015,10 +2023,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -2029,10 +2037,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>57010001</v>
+        <v>56100001</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -2043,10 +2051,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>57040001</v>
+        <v>57010001</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -2057,10 +2065,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -2071,10 +2079,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C82" s="2">
         <v>0</v>
@@ -2085,10 +2093,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" s="2">
         <v>0</v>
@@ -2099,10 +2107,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2113,10 +2121,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>58010001</v>
+        <v>57120001</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C85" s="2">
         <v>0</v>
@@ -2127,10 +2135,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>58040001</v>
+        <v>58010001</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2141,10 +2149,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -2155,10 +2163,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C88" s="2">
         <v>0</v>
@@ -2169,10 +2177,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2183,10 +2191,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>59010001</v>
+        <v>58110001</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
@@ -2197,10 +2205,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2211,10 +2219,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C92" s="2">
         <v>0</v>
@@ -2225,10 +2233,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2239,10 +2247,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
@@ -2253,10 +2261,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2267,10 +2275,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2281,10 +2289,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2295,10 +2303,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -2309,10 +2317,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
@@ -2323,10 +2331,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2337,10 +2345,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
-        <v>60010001</v>
+        <v>59220001</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
@@ -2351,10 +2359,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
@@ -2365,10 +2373,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
@@ -2379,10 +2387,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C104" s="2">
         <v>0</v>
@@ -2393,10 +2401,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C105" s="2">
         <v>0</v>
@@ -2407,10 +2415,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
-        <v>61020001</v>
+        <v>60110001</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C106" s="2">
         <v>0</v>
@@ -2421,10 +2429,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -2435,10 +2443,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -2449,10 +2457,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
@@ -2463,10 +2471,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -2477,10 +2485,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C111" s="2">
         <v>0</v>
@@ -2491,10 +2499,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C112" s="2">
         <v>0</v>
@@ -2505,10 +2513,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C113" s="2">
         <v>0</v>
@@ -2519,22 +2527,36 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
+        <v>61160001</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C114" s="2">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
         <v>61180001</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B115" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C114" s="2">
-        <v>0</v>
-      </c>
-      <c r="D114" s="2">
+      <c r="C115" s="2">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D92" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D39">
-    <sortCondition ref="A34:A39"/>
+  <autoFilter ref="A4:D93" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D40">
+    <sortCondition ref="A35:A40"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583E4A20-58CD-4F70-B6DD-11808E6E8C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22081D1-9333-4EF1-B034-6C7FC8FB895E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>203002011</v>
+        <v>216001001</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>149</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F076BE1-5596-43E7-8C15-EBC713484153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788642F6-39AF-46E2-989D-087951DC7E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,10 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>怪物韧性被打空对自己释放易伤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>冰弹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -148,26 +144,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001011,1001021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002011,1002021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1004011,1004021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14001011,14001021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3002011,3002021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>22201,22202,22203,22204,22205</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -216,10 +192,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>僵尸等级1-普攻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>僵尸等级3-普攻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -261,6 +233,72 @@
   </si>
   <si>
     <t>11002001,11002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级3-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>骷髅怪等级5远程-普攻</t>
+  </si>
+  <si>
+    <t>骷髅怪等级6远程-普攻</t>
+  </si>
+  <si>
+    <t>1003001,1003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001001,1001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002001,1002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1004001,1004002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1005001,1005002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1006001,1006002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14001001,14001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3002001,3002002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血鬼3-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼等级3-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女妖精英-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4003001,4003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13003001,13003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8001001,8001002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -319,7 +357,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,12 +378,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79979857783745845"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +412,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -395,9 +427,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -681,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -773,7 +802,7 @@
         <v>95000101</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
         <v>0</v>
@@ -801,10 +830,10 @@
         <v>20021</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -815,10 +844,10 @@
         <v>20022</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -829,10 +858,10 @@
         <v>20023</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -840,13 +869,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>25010001</v>
+        <v>201001011</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -854,13 +883,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>201001011</v>
+        <v>201002011</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -868,13 +897,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>201002011</v>
+        <v>201003001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -885,10 +914,10 @@
         <v>201004011</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -896,13 +925,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>214001011</v>
+        <v>201005001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -910,13 +939,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>203002011</v>
+        <v>201006001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -924,13 +953,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>216001001</v>
+        <v>214001011</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -940,11 +969,11 @@
       <c r="A19" s="1">
         <v>203001001</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>46</v>
+      <c r="B19" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -952,13 +981,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>203003001</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>47</v>
+        <v>203002011</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -966,13 +995,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>204001001</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>48</v>
+        <v>203003001</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -980,13 +1009,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>204002001</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>49</v>
+        <v>216001001</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -994,13 +1023,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>211001001</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>50</v>
+        <v>208001001</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1008,106 +1037,176 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
+        <v>204001001</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>204002001</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>204003001</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>211001001</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
         <v>211002001</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2">
-        <v>10201</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2">
-        <v>10202</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="2">
+      <c r="B28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2">
-        <v>10301</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="A29" s="1">
+        <v>213003001</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
+        <v>10101</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>10102</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>10201</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>10202</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
         <v>10302</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B35" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="C35" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D30" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:D30">
-    <sortCondition ref="A25:A30"/>
+  <autoFilter ref="A4:D35" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:D35">
+    <sortCondition ref="A30:A35"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788642F6-39AF-46E2-989D-087951DC7E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A16E06-E2E8-4081-A863-4C71437048D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -299,6 +299,10 @@
   </si>
   <si>
     <t>8001001,8001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物破韧后受到伤害增加</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -710,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -869,13 +873,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>201001011</v>
+        <v>25010001</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -883,13 +887,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>201002011</v>
+        <v>201001011</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -897,13 +901,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>201003001</v>
+        <v>201002011</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -911,13 +915,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>201004011</v>
+        <v>201003001</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -925,13 +929,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>201005001</v>
+        <v>201004011</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -939,13 +943,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>201006001</v>
+        <v>201005001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -953,13 +957,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>214001011</v>
+        <v>201006001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -967,13 +971,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>203001001</v>
+        <v>214001011</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -981,13 +985,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>203002011</v>
+        <v>203001001</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -995,13 +999,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>203003001</v>
+        <v>203002011</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1009,13 +1013,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>216001001</v>
+        <v>203003001</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1023,13 +1027,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>208001001</v>
+        <v>216001001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1037,13 +1041,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>204001001</v>
+        <v>208001001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1051,13 +1055,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>204002001</v>
+        <v>204001001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1065,13 +1069,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>204003001</v>
+        <v>204002001</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1079,13 +1083,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>211001001</v>
+        <v>204003001</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1093,13 +1097,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>211002001</v>
+        <v>211001001</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1107,38 +1111,38 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
+        <v>211002001</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>213003001</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B30" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="2">
+      <c r="D30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>30</v>
@@ -1149,10 +1153,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>30</v>
@@ -1163,13 +1167,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D33" s="2">
         <v>0</v>
@@ -1177,13 +1181,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1191,22 +1195,36 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
         <v>10302</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D36" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D35" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:D35">
-    <sortCondition ref="A30:A35"/>
+  <autoFilter ref="A4:D36" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D36">
+    <sortCondition ref="A31:A36"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A16E06-E2E8-4081-A863-4C71437048D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5716633-7784-4C45-8790-820E4709F6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -303,6 +303,10 @@
   </si>
   <si>
     <t>怪物破韧后受到伤害增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷暴云</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -714,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -873,27 +877,27 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>25010001</v>
+        <v>20033</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="1">
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>31000010</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>201001011</v>
+        <v>25010001</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -901,13 +905,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>201002011</v>
+        <v>201001011</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -915,13 +919,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>201003001</v>
+        <v>201002011</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -929,13 +933,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>201004011</v>
+        <v>201003001</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -943,13 +947,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>201005001</v>
+        <v>201004011</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -957,13 +961,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>201006001</v>
+        <v>201005001</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -971,13 +975,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>214001011</v>
+        <v>201006001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -985,13 +989,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>203001001</v>
+        <v>214001011</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -999,13 +1003,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>203002011</v>
+        <v>203001001</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1013,13 +1017,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>203003001</v>
+        <v>203002011</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1027,13 +1031,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>216001001</v>
+        <v>203003001</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1041,13 +1045,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>208001001</v>
+        <v>216001001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1055,13 +1059,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>204001001</v>
+        <v>208001001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1069,13 +1073,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>204002001</v>
+        <v>204001001</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1083,13 +1087,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>204003001</v>
+        <v>204002001</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1097,13 +1101,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>211001001</v>
+        <v>204003001</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1111,13 +1115,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>211002001</v>
+        <v>211001001</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1125,38 +1129,38 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
+        <v>211002001</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
         <v>213003001</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B31" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="2">
+      <c r="D31" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>30</v>
@@ -1167,10 +1171,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>30</v>
@@ -1181,13 +1185,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D34" s="2">
         <v>0</v>
@@ -1195,13 +1199,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1209,22 +1213,36 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
         <v>10302</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D37" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D36" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A31:D36">
-    <sortCondition ref="A31:A36"/>
+  <autoFilter ref="A4:D37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:D37">
+    <sortCondition ref="A32:A37"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5716633-7784-4C45-8790-820E4709F6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AB6FF2-FEBA-4B98-BB4F-9C666B4A99E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -307,6 +307,22 @@
   </si>
   <si>
     <t>雷暴云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊等级1-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊等级3-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7001001,7001002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7003001,7003002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -365,7 +381,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,6 +402,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79979857783745845"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79976805932798245"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,7 +442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -435,6 +457,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -718,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1156,39 +1181,39 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="2">
+      <c r="A32" s="8">
+        <v>207001001</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D32" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="2">
+      <c r="A33" s="8">
+        <v>207003001</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>30</v>
@@ -1199,13 +1224,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10202</v>
+        <v>10102</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
@@ -1213,13 +1238,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D36" s="2">
         <v>0</v>
@@ -1227,22 +1252,50 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
+        <v>10202</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
         <v>10302</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D39" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A32:D37">
-    <sortCondition ref="A32:A37"/>
+  <autoFilter ref="A4:D39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D39">
+    <sortCondition ref="A34:A39"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AB6FF2-FEBA-4B98-BB4F-9C666B4A99E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03743191-D596-47F1-B113-85F96C0C5EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -323,6 +323,14 @@
   </si>
   <si>
     <t>7003001,7003002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熊等级2-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7002001,7002002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -1196,38 +1204,38 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
+        <v>207002001</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>207003001</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B34" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C34" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>30</v>
@@ -1238,10 +1246,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>30</v>
@@ -1252,13 +1260,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
@@ -1266,13 +1274,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1280,22 +1288,36 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
         <v>10302</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D40" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:D39">
-    <sortCondition ref="A34:A39"/>
+  <autoFilter ref="A4:D40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D40">
+    <sortCondition ref="A35:A40"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03743191-D596-47F1-B113-85F96C0C5EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0DDACB-2766-428B-9716-FA8ABE39569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -332,6 +332,13 @@
   <si>
     <t>7002001,7002002</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤物-火龙-普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毁灭风暴</t>
   </si>
 </sst>
 </file>
@@ -389,7 +396,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -416,6 +423,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79976805932798245"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,7 +463,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -468,6 +481,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -751,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -924,13 +940,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>25010001</v>
+        <v>20104</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1">
-        <v>0</v>
+        <v>21201</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -938,13 +954,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>201001011</v>
+        <v>25010001</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -952,13 +968,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>201002011</v>
+        <v>201001011</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -966,13 +982,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>201003001</v>
+        <v>201002011</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -980,13 +996,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>201004011</v>
+        <v>201003001</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -994,13 +1010,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>201005001</v>
+        <v>201004011</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1008,13 +1024,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>201006001</v>
+        <v>201005001</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1022,13 +1038,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>214001011</v>
+        <v>201006001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1036,13 +1052,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>203001001</v>
+        <v>214001011</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1050,13 +1066,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>203002011</v>
+        <v>203001001</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
@@ -1064,13 +1080,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>203003001</v>
+        <v>203002011</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1078,13 +1094,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>216001001</v>
+        <v>203003001</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1092,13 +1108,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>208001001</v>
+        <v>216001001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1106,13 +1122,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
-        <v>204001001</v>
+        <v>208001001</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1120,13 +1136,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>204002001</v>
+        <v>204001001</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1134,13 +1150,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
-        <v>204003001</v>
+        <v>204002001</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1148,13 +1164,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>211001001</v>
+        <v>204003001</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -1162,13 +1178,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>211002001</v>
+        <v>211001001</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -1176,27 +1192,27 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
+        <v>211002001</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>213003001</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>207001001</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -1204,13 +1220,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
-        <v>207002001</v>
+        <v>207001001</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -1218,52 +1234,52 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
+        <v>207002001</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
         <v>207003001</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
-        <v>10101</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>10102</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="2">
+      <c r="A36" s="8">
+        <v>200801001</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="6">
+        <v>801001</v>
+      </c>
+      <c r="D36" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>30</v>
@@ -1274,13 +1290,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>10202</v>
+        <v>10102</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
@@ -1288,13 +1304,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>10301</v>
+        <v>10201</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1302,22 +1318,50 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
+        <v>10202</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>10301</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
         <v>10302</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D42" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D40" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:D40">
-    <sortCondition ref="A35:A40"/>
+  <autoFilter ref="A4:D42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A37:D42">
+    <sortCondition ref="A37:A42"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBCD1ECF-6EB3-4A62-BD50-E9DF381462AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B780F56-66B7-4B01-8500-4AD5F4BD1E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -355,11 +355,11 @@
     <t>沉沦魔等级4-普攻</t>
   </si>
   <si>
-    <t>11003001,11003000</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>11004001,11004000</t>
+    <t>11003001,11003002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>11004001,11004002</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B780F56-66B7-4B01-8500-4AD5F4BD1E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D861DA-A944-4253-B21C-CAC7D99D9CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -360,6 +360,14 @@
   </si>
   <si>
     <t>11004001,11004002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>强盗等级4-普攻</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004001,2004002</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -804,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -1144,14 +1152,14 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>214001011</v>
+      <c r="A25" s="11">
+        <v>202004001</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
@@ -1159,13 +1167,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>203001001</v>
+        <v>214001011</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D26" s="3">
         <v>0</v>
@@ -1173,13 +1181,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>203002011</v>
+        <v>203001001</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
@@ -1187,13 +1195,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>203003001</v>
+        <v>203002011</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -1201,13 +1209,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>204001001</v>
+        <v>203003001</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -1215,13 +1223,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>204002001</v>
+        <v>204001001</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D30" s="3">
         <v>0</v>
@@ -1229,27 +1237,27 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
+        <v>204002001</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
         <v>204003001</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C32" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="11">
-        <v>205001001</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
@@ -1257,13 +1265,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="11">
-        <v>205003001</v>
+        <v>205001001</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="3">
         <v>0</v>
@@ -1271,13 +1279,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="11">
-        <v>205004001</v>
+        <v>205003001</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3">
         <v>0</v>
@@ -1285,27 +1293,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="11">
+        <v>205004001</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="11">
         <v>206001001</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B36" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C36" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="6">
-        <v>207001001</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="D36" s="3">
         <v>0</v>
@@ -1313,13 +1321,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
-        <v>207002001</v>
+        <v>207001001</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D37" s="3">
         <v>0</v>
@@ -1327,41 +1335,41 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
+        <v>207002001</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="6">
         <v>207003001</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B39" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C39" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
         <v>208001001</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B40" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C40" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="11">
-        <v>209001001</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>96</v>
       </c>
       <c r="D40" s="3">
         <v>0</v>
@@ -1369,27 +1377,27 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="11">
+        <v>209001001</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="11">
         <v>209003001</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B42" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C42" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="D41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>211001001</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="D42" s="3">
         <v>0</v>
@@ -1397,27 +1405,27 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
+        <v>211001001</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
         <v>211002001</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C44" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="11">
-        <v>211003001</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
@@ -1425,27 +1433,27 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="11">
+        <v>211003001</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="11">
         <v>211004001</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B46" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>213003001</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>57</v>
       </c>
       <c r="D46" s="3">
         <v>0</v>
@@ -1453,52 +1461,52 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
+        <v>213003001</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
         <v>216001001</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C48" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="6">
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="6">
         <v>200801001</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B49" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C49" s="5">
         <v>801001</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="1">
-        <v>10101</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="D49" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
-        <v>10102</v>
+        <v>10101</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>66</v>
@@ -1509,10 +1517,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>10201</v>
+        <v>10102</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>66</v>
@@ -1523,13 +1531,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
-        <v>10202</v>
+        <v>10201</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -1537,13 +1545,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
-        <v>10301</v>
+        <v>10202</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -1551,22 +1559,36 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
+        <v>10301</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
         <v>10302</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C55" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="1">
+      <c r="D55" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A49:D54">
-    <sortCondition ref="A49:A54"/>
+  <autoFilter ref="A4:D55" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A50:D55">
+    <sortCondition ref="A50:A55"/>
   </sortState>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D861DA-A944-4253-B21C-CAC7D99D9CF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264A854-A478-4705-9454-86301A989806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_skill_act_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_act_v8!$A$4:$D$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="124">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -204,9 +204,6 @@
     <t>11002001,11002002</t>
   </si>
   <si>
-    <t>吸血鬼3-普攻</t>
-  </si>
-  <si>
     <t>13003001,13003002</t>
   </si>
   <si>
@@ -368,6 +365,81 @@
   </si>
   <si>
     <t>2004001,2004002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>5002001,5002002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>狼人等级2-普攻</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>羊头狼人等级2-普攻</t>
+  </si>
+  <si>
+    <t>羊头狼人等级3-普攻</t>
+  </si>
+  <si>
+    <t>羊头狼人等级4-普攻</t>
+  </si>
+  <si>
+    <t>6002001,6002002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>6003001,6003002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>6004001,6004002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血鬼等级1-普攻</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血鬼等级2-普攻</t>
+  </si>
+  <si>
+    <t>吸血鬼等级3-普攻</t>
+  </si>
+  <si>
+    <t>吸血鬼等级4-普攻</t>
+  </si>
+  <si>
+    <t>13001001,13001002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>13002001,13002002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>13004001,13004002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>压迫者等级1-普攻</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>压迫者等级2-普攻</t>
+  </si>
+  <si>
+    <t>压迫者等级3-普攻</t>
+  </si>
+  <si>
+    <t>压迫者等级4-普攻</t>
+  </si>
+  <si>
+    <t>11001001,11001002</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>11002001,11002002</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -433,7 +505,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,12 +521,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79976805932798245"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79973754081850645"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,11 +569,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -520,10 +586,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -533,7 +596,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -812,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -934,7 +997,7 @@
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="3">
@@ -948,7 +1011,7 @@
       <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="3">
@@ -962,7 +1025,7 @@
       <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D11" s="3">
@@ -1018,7 +1081,7 @@
       <c r="B15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="3">
@@ -1032,7 +1095,7 @@
       <c r="B16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="3">
@@ -1046,7 +1109,7 @@
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="3">
@@ -1054,14 +1117,14 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>201007001</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="D18" s="3">
         <v>0</v>
@@ -1072,9 +1135,9 @@
         <v>201004011</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D19" s="3">
@@ -1086,9 +1149,9 @@
         <v>201005001</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D20" s="3">
@@ -1100,66 +1163,66 @@
         <v>201006001</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
+        <v>202001001</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="11">
-        <v>202001001</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
+        <v>202002001</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="11">
-        <v>202002001</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>202003001</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="11">
-        <v>202003001</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>85</v>
-      </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="11">
+      <c r="A25" s="3">
         <v>202004001</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
@@ -1172,7 +1235,7 @@
       <c r="B26" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D26" s="3">
@@ -1186,7 +1249,7 @@
       <c r="B27" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="3">
@@ -1200,7 +1263,7 @@
       <c r="B28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D28" s="3">
@@ -1214,7 +1277,7 @@
       <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D29" s="3">
@@ -1228,7 +1291,7 @@
       <c r="B30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D30" s="3">
@@ -1242,7 +1305,7 @@
       <c r="B31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D31" s="3">
@@ -1256,7 +1319,7 @@
       <c r="B32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D32" s="3">
@@ -1264,98 +1327,98 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="11">
+      <c r="A33" s="3">
         <v>205001001</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>205002001</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>205003001</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="11">
-        <v>205003001</v>
-      </c>
-      <c r="B34" s="4" t="s">
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>205004001</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="11">
-        <v>205004001</v>
-      </c>
-      <c r="B35" s="4" t="s">
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>206001001</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="11">
-        <v>206001001</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="6">
-        <v>207001001</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="D37" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="6">
-        <v>207002001</v>
+      <c r="A38" s="3">
+        <v>26002001</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>61</v>
+        <v>105</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="D38" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="6">
-        <v>207003001</v>
+      <c r="A39" s="3">
+        <v>26003001</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>63</v>
+        <v>106</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="D39" s="3">
         <v>0</v>
@@ -1363,41 +1426,41 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>208001001</v>
+        <v>26004001</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>45</v>
+        <v>107</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D40" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="11">
-        <v>209001001</v>
+      <c r="A41" s="3">
+        <v>207001001</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>96</v>
+        <v>57</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="D41" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="11">
-        <v>209003001</v>
+      <c r="A42" s="3">
+        <v>207002001</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>97</v>
+        <v>59</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="D42" s="3">
         <v>0</v>
@@ -1405,13 +1468,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <v>211001001</v>
+        <v>207003001</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>53</v>
+        <v>61</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="D43" s="3">
         <v>0</v>
@@ -1419,41 +1482,41 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <v>211002001</v>
+        <v>208001001</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="D44" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="11">
-        <v>211003001</v>
+      <c r="A45" s="3">
+        <v>209001001</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="D45" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="11">
-        <v>211004001</v>
+      <c r="A46" s="3">
+        <v>209003001</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="D46" s="3">
         <v>0</v>
@@ -1461,13 +1524,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
-        <v>213003001</v>
+        <v>211001001</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="D47" s="3">
         <v>0</v>
@@ -1475,120 +1538,274 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
+        <v>211002001</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>211003001</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>211004001</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>211001001</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>211002001</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <v>211003001</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="3">
+        <v>211004001</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="3">
+        <v>213001001</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="3">
+        <v>213002001</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="3">
+        <v>213003001</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="3">
+        <v>213004001</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="3">
         <v>216001001</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B59" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C59" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="6">
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="3">
         <v>200801001</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B60" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" s="5">
+        <v>801001</v>
+      </c>
+      <c r="D60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>10101</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="5">
-        <v>801001</v>
-      </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>10101</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="C61" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>10102</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="1">
-        <v>10102</v>
-      </c>
-      <c r="B51" s="2" t="s">
+      <c r="C62" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>10201</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="1">
-        <v>10201</v>
-      </c>
-      <c r="B52" s="2" t="s">
+      <c r="C63" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>10202</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="1">
-        <v>10202</v>
-      </c>
-      <c r="B53" s="2" t="s">
+      <c r="C64" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>10301</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="1">
-        <v>10301</v>
-      </c>
-      <c r="B54" s="2" t="s">
+      <c r="C65" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>10302</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="1">
-        <v>10302</v>
-      </c>
-      <c r="B55" s="2" t="s">
+      <c r="C66" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="1">
+      <c r="D66" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D55" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A50:D55">
-    <sortCondition ref="A50:A55"/>
+  <autoFilter ref="A4:D66" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A61:D66">
+    <sortCondition ref="A61:A66"/>
   </sortState>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_act_v8【迷宫-技能-技能动作】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6264A854-A478-4705-9454-86301A989806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7002B20F-44CD-44C0-AE10-D10F7ED2AAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>26002001</v>
+        <v>206002001</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>105</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>26003001</v>
+        <v>206003001</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>106</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
-        <v>26004001</v>
+        <v>206004001</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>107</v>
